--- a/reports/latest/android/Excel/Failed_Test_Cases.xlsx
+++ b/reports/latest/android/Excel/Failed_Test_Cases.xlsx
@@ -482,7 +482,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -543,7 +543,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>TC_GEN_007</t>
+          <t>TC_GEN_003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>test_navigation_between_screens</t>
+          <t>test_home_page_load</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -568,17 +568,17 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:03:31</t>
+          <t>2026-06-23 16:31:25</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="5d941e00-69e0-4516-8ef1-9aad1eb798d1")&gt;
+          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="780dd579-ad7d-405b-92c8-18302ab263c6")&gt;
     @pytest.fixture(scope="function")
     def auth_driver(driver):
         """Fixture to launch app and log in automatically with test credentials."""
@@ -609,8 +609,8 @@
 /opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:492: in execute
     self.error_handler.check_response(response)
 _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
-self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7f904310df50&gt;
-response = {'status': 500, 'value': '{"value":{"error":"unknown error","message":"Timed out after 10504ms waiting for the root Ac...r2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:327)\\n\\t... 33 more\\n"}}'}
+self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7f052231b410&gt;
+response = {'status': 500, 'value': '{"value":{"error":"unknown error","message":"Timed out after 10510ms waiting for the root Ac...r2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:327)\\n\\t... 33 more\\n"}}'}
     def check_response(self, response: Dict[str, Any]) -&gt; None:
         """
         https://www.w3.org/TR/webdriver/#errors
@@ -651,9 +651,9 @@
                 alert_text=value.get('data'),
             )
 &gt;       raise exception_class(msg=message, stacktrace=format_stacktrace(stacktrace))
-E       selenium.common.exceptions.WebDriverException: Message: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
+E       selenium.common.exceptions.WebDriverException: Message: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
 E       Stacktrace:
-E       io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
+E       io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
 E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:366)
 E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodes(AccessibilityNodeInfoDumper.java:378)
 E       	at io.appium.uiautomator2.utils.ElementLocationHelpers.getXPathNodeMatch(ElementLocationHelpers.java:124)
@@ -688,7 +688,7 @@
 E       	at io.netty.util.internal.ThreadExecutorMap$2.run(ThreadExecutorMap.java:74)
 E       	at io.netty.util.concurrent.FastThreadLocalRunnable.run(FastThreadLocalRunnable.java:30)
 E       	at java.lang.Thread.run(Thread.java:919)
-E       Caused by: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
+E       Caused by: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
 E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getActiveWindowRoot(AXWindowHelpers.java:107)
 E       	at io.appium.uiautomator2.utils.AXWindowHelpers.retrieveWindowRoots(AXWindowHelpers.java:87)
 E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getCachedWindowRoots(AXWindowHelpers.java:68)

--- a/reports/latest/android/Excel/Failed_Test_Cases.xlsx
+++ b/reports/latest/android/Excel/Failed_Test_Cases.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,15 +37,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -62,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="002A4D7C"/>
         <bgColor rgb="002A4D7C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
-        <bgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,20 +84,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,17 +457,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="9568" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -537,165 +517,6 @@
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Failure Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>TC_GEN_003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>test_home_page_load</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>29.94</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 16:31:25</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="780dd579-ad7d-405b-92c8-18302ab263c6")&gt;
-    @pytest.fixture(scope="function")
-    def auth_driver(driver):
-        """Fixture to launch app and log in automatically with test credentials."""
-        time.sleep(5)
-        login_page = LoginPage(driver)
-        print("[MobileTest] Performing E2E test login...")
-&gt;       login_page.login("testfarmer@example.com", "TestFarmer123!")
-tests/mobile_e2e/test_suites/test_features.py:14: 
-_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
-tests/mobile_e2e/pages/login_page.py:14: in login
-    self.send_keys(self.EMAIL_INPUT, email)
-tests/mobile_e2e/pages/base_page.py:31: in send_keys
-    element = self.wait_for_element(locator)
-              ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-tests/mobile_e2e/pages/base_page.py:22: in wait_for_element
-    raise e
-tests/mobile_e2e/pages/base_page.py:17: in wait_for_element
-    return WebDriverWait(self.driver, self.timeout).until(
-/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/support/wait.py:112: in until
-    value = method(self._driver)
-            ^^^^^^^^^^^^^^^^^^^^
-/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/support/expected_conditions.py:188: in _predicate
-    return _element_if_visible(driver.find_element(*locator))
-                               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:899: in find_element
-    return self.execute(Command.FIND_ELEMENT, {"using": by, "value": value})["value"]
-           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:492: in execute
-    self.error_handler.check_response(response)
-_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
-self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7f052231b410&gt;
-response = {'status': 500, 'value': '{"value":{"error":"unknown error","message":"Timed out after 10510ms waiting for the root Ac...r2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:327)\\n\\t... 33 more\\n"}}'}
-    def check_response(self, response: Dict[str, Any]) -&gt; None:
-        """
-        https://www.w3.org/TR/webdriver/#errors
-        """
-        payload = response.get('value', '')
-        if isinstance(payload, dict):
-            payload_dict = payload
-        else:
-            try:
-                payload_dict = json.loads(payload)
-            except (json.JSONDecodeError, TypeError):
-                return
-            if not isinstance(payload_dict, dict):
-                return
-        value = payload_dict.get('value')
-        if not isinstance(value, dict):
-            return
-        error = value.get('error')
-        if not error:
-            return
-        message = value.get('message', error)
-        stacktrace = value.get('stacktrace', '')
-        # In theory, we should also be checking HTTP status codes.
-        # Java client, for example, prints a warning if the actual `error`
-        # value does not match to the response's HTTP status code.
-        exception_class: Type[sel_exceptions.WebDriverException] = ERROR_TO_EXC_MAPPING.get(
-            error, sel_exceptions.WebDriverException
-        )
-        if exception_class is sel_exceptions.WebDriverException and message:
-            if message == 'No such context found.':
-                exception_class = appium_exceptions.NoSuchContextException
-            elif message == 'That command could not be executed in the current context.':
-                exception_class = appium_exceptions.InvalidSwitchToTargetException
-        if exception_class is sel_exceptions.UnexpectedAlertPresentException:
-            raise sel_exceptions.UnexpectedAlertPresentException(
-                msg=message,
-                stacktrace=format_stacktrace(stacktrace),
-                alert_text=value.get('data'),
-            )
-&gt;       raise exception_class(msg=message, stacktrace=format_stacktrace(stacktrace))
-E       selenium.common.exceptions.WebDriverException: Message: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
-E       Stacktrace:
-E       io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
-E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:366)
-E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodes(AccessibilityNodeInfoDumper.java:378)
-E       	at io.appium.uiautomator2.utils.ElementLocationHelpers.getXPathNodeMatch(ElementLocationHelpers.java:124)
-E       	at io.appium.uiautomator2.utils.ElementLocationHelpers.findElement(ElementLocationHelpers.java:151)
-E       	at io.appium.uiautomator2.handler.FindElement.safeHandle(FindElement.java:60)
-E       	at io.appium.uiautomator2.handler.request.SafeRequestHandler.handle(SafeRequestHandler.java:59)
-E       	at io.appium.uiautomator2.server.AppiumServlet.handleRequest(AppiumServlet.java:267)
-E       	at io.appium.uiautomator2.server.AppiumServlet.handleHttpRequest(AppiumServlet.java:261)
-E       	at io.appium.uiautomator2.http.ServerHandler.channelRead(ServerHandler.java:77)
-E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:357)
-E       	at io.netty.handler.codec.MessageToMessageDecoder.channelRead(MessageToMessageDecoder.java:107)
-E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:357)
-E       	at io.netty.channel.CombinedChannelDuplexHandler$DelegatingChannelHandlerContext.fireChannelRead(CombinedChannelDuplexHandler.java:434)
-E       	at io.netty.handler.codec.ByteToMessageDecoder.fireChannelRead(ByteToMessageDecoder.java:361)
-E       	at io.netty.handler.codec.ByteToMessageDecoder.channelRead(ByteToMessageDecoder.java:325)
-E       	at io.netty.channel.CombinedChannelDuplexHandler.channelRead(CombinedChannelDuplexHandler.java:249)
-E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:355)
-E       	at io.netty.handler.timeout.IdleStateHandler.channelRead(IdleStateHandler.java:288)
-E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:355)
-E       	at io.netty.channel.DefaultChannelPipeline$HeadContext.channelRead(DefaultChannelPipeline.java:1429)
-E       	at io.netty.channel.DefaultChannelPipeline.fireChannelRead(DefaultChannelPipeline.java:918)
-E       	at io.netty.channel.nio.AbstractNioByteChannel$NioByteUnsafe.read(AbstractNioByteChannel.java:176)
-E       	at io.netty.channel.nio.AbstractNioChannel$AbstractNioUnsafe.handle(AbstractNioChannel.java:445)
-E       	at io.netty.channel.nio.NioIoHandler$DefaultNioRegistration.handle(NioIoHandler.java:388)
-E       	at io.netty.channel.nio.NioIoHandler.processSelectedKey(NioIoHandler.java:596)
-E       	at io.netty.channel.nio.NioIoHandler.processSelectedKeysOptimized(NioIoHandler.java:571)
-E       	at io.netty.channel.nio.NioIoHandler.processSelectedKeys(NioIoHandler.java:512)
-E       	at io.netty.channel.nio.NioIoHandler.run(NioIoHandler.java:484)
-E       	at io.netty.channel.SingleThreadIoEventLoop.runIo(SingleThreadIoEventLoop.java:225)
-E       	at io.netty.channel.SingleThreadIoEventLoop.run(SingleThreadIoEventLoop.java:196)
-E       	at io.netty.util.concurrent.SingleThreadEventExecutor$5.run(SingleThreadEventExecutor.java:1195)
-E       	at io.netty.util.internal.ThreadExecutorMap$2.run(ThreadExecutorMap.java:74)
-E       	at io.netty.util.concurrent.FastThreadLocalRunnable.run(FastThreadLocalRunnable.java:30)
-E       	at java.lang.Thread.run(Thread.java:919)
-E       Caused by: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
-E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getActiveWindowRoot(AXWindowHelpers.java:107)
-E       	at io.appium.uiautomator2.utils.AXWindowHelpers.retrieveWindowRoots(AXWindowHelpers.java:87)
-E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getCachedWindowRoots(AXWindowHelpers.java:68)
-E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.toStream(AccessibilityNodeInfoDumper.java:228)
-E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:327)
-E       	... 33 more
-/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/appium/webdriver/errorhandler.py:125: WebDriverException</t>
         </is>
       </c>
     </row>

--- a/reports/latest/android/Excel/Failed_Test_Cases.xlsx
+++ b/reports/latest/android/Excel/Failed_Test_Cases.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +37,15 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +62,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="002A4D7C"/>
         <bgColor rgb="002A4D7C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
+        <bgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,13 +97,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -457,17 +477,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="9450" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -517,6 +537,163 @@
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Failure Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TC_GEN_001</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>test_auth_client_validation</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>37.13</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 01:02:14</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="00625872-fc8f-4afa-8e82-501673e0c66e")&gt;
+    def test_auth_client_validation(driver):
+        """Test that login validation fails when submitting empty fields on mobile."""
+        time.sleep(5)  # Wait for app to boot on emulator
+        login_page = LoginPage(driver)
+        login_page.capture_screenshot("mobile_login_screen_load")
+        # Submit empty fields
+&gt;       login_page.click(login_page.SUBMIT_BUTTON)
+tests/mobile_e2e/test_suites/test_auth.py:12: 
+_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
+tests/mobile_e2e/pages/base_page.py:26: in click
+    element = self.wait_for_element(locator)
+              ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+tests/mobile_e2e/pages/base_page.py:22: in wait_for_element
+    raise e
+tests/mobile_e2e/pages/base_page.py:17: in wait_for_element
+    return WebDriverWait(self.driver, self.timeout).until(
+/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/support/wait.py:112: in until
+    value = method(self._driver)
+            ^^^^^^^^^^^^^^^^^^^^
+/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/support/expected_conditions.py:188: in _predicate
+    return _element_if_visible(driver.find_element(*locator))
+                               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:899: in find_element
+    return self.execute(Command.FIND_ELEMENT, {"using": by, "value": value})["value"]
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:492: in execute
+    self.error_handler.check_response(response)
+_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
+self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7fc0b4b71310&gt;
+response = {'status': 500, 'value': '{"value":{"error":"unknown error","message":"io.appium.uiautomator2.common.exceptions.UiAuto...r2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath1(AccessibilityNodeInfoDumper.java:279)\\n\\t... 33 more\\n"}}'}
+    def check_response(self, response: Dict[str, Any]) -&gt; None:
+        """
+        https://www.w3.org/TR/webdriver/#errors
+        """
+        payload = response.get('value', '')
+        if isinstance(payload, dict):
+            payload_dict = payload
+        else:
+            try:
+                payload_dict = json.loads(payload)
+            except (json.JSONDecodeError, TypeError):
+                return
+            if not isinstance(payload_dict, dict):
+                return
+        value = payload_dict.get('value')
+        if not isinstance(value, dict):
+            return
+        error = value.get('error')
+        if not error:
+            return
+        message = value.get('message', error)
+        stacktrace = value.get('stacktrace', '')
+        # In theory, we should also be checking HTTP status codes.
+        # Java client, for example, prints a warning if the actual `error`
+        # value does not match to the response's HTTP status code.
+        exception_class: Type[sel_exceptions.WebDriverException] = ERROR_TO_EXC_MAPPING.get(
+            error, sel_exceptions.WebDriverException
+        )
+        if exception_class is sel_exceptions.WebDriverException and message:
+            if message == 'No such context found.':
+                exception_class = appium_exceptions.NoSuchContextException
+            elif message == 'That command could not be executed in the current context.':
+                exception_class = appium_exceptions.InvalidSwitchToTargetException
+        if exception_class is sel_exceptions.UnexpectedAlertPresentException:
+            raise sel_exceptions.UnexpectedAlertPresentException(
+                msg=message,
+                stacktrace=format_stacktrace(stacktrace),
+                alert_text=value.get('data'),
+            )
+&gt;       raise exception_class(msg=message, stacktrace=format_stacktrace(stacktrace))
+E       selenium.common.exceptions.WebDriverException: Message: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
+E       Stacktrace:
+E       io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
+E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath1(AccessibilityNodeInfoDumper.java:306)
+E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodes(AccessibilityNodeInfoDumper.java:377)
+E       	at io.appium.uiautomator2.utils.ElementLocationHelpers.getXPathNodeMatch(ElementLocationHelpers.java:124)
+E       	at io.appium.uiautomator2.utils.ElementLocationHelpers.findElement(ElementLocationHelpers.java:151)
+E       	at io.appium.uiautomator2.handler.FindElement.safeHandle(FindElement.java:60)
+E       	at io.appium.uiautomator2.handler.request.SafeRequestHandler.handle(SafeRequestHandler.java:59)
+E       	at io.appium.uiautomator2.server.AppiumServlet.handleRequest(AppiumServlet.java:267)
+E       	at io.appium.uiautomator2.server.AppiumServlet.handleHttpRequest(AppiumServlet.java:261)
+E       	at io.appium.uiautomator2.http.ServerHandler.channelRead(ServerHandler.java:77)
+E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:357)
+E       	at io.netty.handler.codec.MessageToMessageDecoder.channelRead(MessageToMessageDecoder.java:107)
+E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:357)
+E       	at io.netty.channel.CombinedChannelDuplexHandler$DelegatingChannelHandlerContext.fireChannelRead(CombinedChannelDuplexHandler.java:434)
+E       	at io.netty.handler.codec.ByteToMessageDecoder.fireChannelRead(ByteToMessageDecoder.java:361)
+E       	at io.netty.handler.codec.ByteToMessageDecoder.channelRead(ByteToMessageDecoder.java:325)
+E       	at io.netty.channel.CombinedChannelDuplexHandler.channelRead(CombinedChannelDuplexHandler.java:249)
+E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:355)
+E       	at io.netty.handler.timeout.IdleStateHandler.channelRead(IdleStateHandler.java:288)
+E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:355)
+E       	at io.netty.channel.DefaultChannelPipeline$HeadContext.channelRead(DefaultChannelPipeline.java:1429)
+E       	at io.netty.channel.DefaultChannelPipeline.fireChannelRead(DefaultChannelPipeline.java:918)
+E       	at io.netty.channel.nio.AbstractNioByteChannel$NioByteUnsafe.read(AbstractNioByteChannel.java:176)
+E       	at io.netty.channel.nio.AbstractNioChannel$AbstractNioUnsafe.handle(AbstractNioChannel.java:445)
+E       	at io.netty.channel.nio.NioIoHandler$DefaultNioRegistration.handle(NioIoHandler.java:388)
+E       	at io.netty.channel.nio.NioIoHandler.processSelectedKey(NioIoHandler.java:596)
+E       	at io.netty.channel.nio.NioIoHandler.processSelectedKeysOptimized(NioIoHandler.java:571)
+E       	at io.netty.channel.nio.NioIoHandler.processSelectedKeys(NioIoHandler.java:512)
+E       	at io.netty.channel.nio.NioIoHandler.run(NioIoHandler.java:484)
+E       	at io.netty.channel.SingleThreadIoEventLoop.runIo(SingleThreadIoEventLoop.java:225)
+E       	at io.netty.channel.SingleThreadIoEventLoop.run(SingleThreadIoEventLoop.java:196)
+E       	at io.netty.util.concurrent.SingleThreadEventExecutor$5.run(SingleThreadEventExecutor.java:1195)
+E       	at io.netty.util.internal.ThreadExecutorMap$2.run(ThreadExecutorMap.java:74)
+E       	at io.netty.util.concurrent.FastThreadLocalRunnable.run(FastThreadLocalRunnable.java:30)
+E       	at java.lang.Thread.run(Thread.java:919)
+E       Caused by: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
+E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getActiveWindowRoot(AXWindowHelpers.java:107)
+E       	at io.appium.uiautomator2.utils.AXWindowHelpers.retrieveWindowRoots(AXWindowHelpers.java:87)
+E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getCachedWindowRoots(AXWindowHelpers.java:68)
+E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.toStream(AccessibilityNodeInfoDumper.java:228)
+E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath1(AccessibilityNodeInfoDumper.java:279)
+E       	... 33 more
+/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/appium/webdriver/errorhandler.py:125: WebDriverException</t>
         </is>
       </c>
     </row>

--- a/reports/latest/android/Excel/Failed_Test_Cases.xlsx
+++ b/reports/latest/android/Excel/Failed_Test_Cases.xlsx
@@ -482,12 +482,12 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="9450" customWidth="1" min="8" max="8"/>
+    <col width="9433" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -543,7 +543,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>TC_GEN_001</t>
+          <t>TC_GEN_002</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>test_auth_client_validation</t>
+          <t>test_auth_invalid_credentials</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -568,27 +568,27 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 01:02:14</t>
+          <t>2026-06-24 01:32:38</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="00625872-fc8f-4afa-8e82-501673e0c66e")&gt;
-    def test_auth_client_validation(driver):
-        """Test that login validation fails when submitting empty fields on mobile."""
-        time.sleep(5)  # Wait for app to boot on emulator
+          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="8df9b57d-e778-4b63-9dc7-3ab099e509dd")&gt;
+    def test_auth_invalid_credentials(driver):
+        """Test that login with invalid credentials displays an error on mobile."""
+        time.sleep(3)
         login_page = LoginPage(driver)
-        login_page.capture_screenshot("mobile_login_screen_load")
-        # Submit empty fields
-&gt;       login_page.click(login_page.SUBMIT_BUTTON)
-tests/mobile_e2e/test_suites/test_auth.py:12: 
+&gt;       login_page.login("nonexistent_farmer@kisan.com", "WrongPass123!")
+tests/mobile_e2e/test_suites/test_auth.py:25: 
 _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
-tests/mobile_e2e/pages/base_page.py:26: in click
+tests/mobile_e2e/pages/login_page.py:14: in login
+    self.send_keys(self.EMAIL_INPUT, email)
+tests/mobile_e2e/pages/base_page.py:31: in send_keys
     element = self.wait_for_element(locator)
               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
 tests/mobile_e2e/pages/base_page.py:22: in wait_for_element
@@ -607,7 +607,7 @@
 /opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:492: in execute
     self.error_handler.check_response(response)
 _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
-self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7fc0b4b71310&gt;
+self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7f2b9cc46990&gt;
 response = {'status': 500, 'value': '{"value":{"error":"unknown error","message":"io.appium.uiautomator2.common.exceptions.UiAuto...r2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath1(AccessibilityNodeInfoDumper.java:279)\\n\\t... 33 more\\n"}}'}
     def check_response(self, response: Dict[str, Any]) -&gt; None:
         """

--- a/reports/latest/android/Excel/Failed_Test_Cases.xlsx
+++ b/reports/latest/android/Excel/Failed_Test_Cases.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,15 +37,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -62,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="002A4D7C"/>
         <bgColor rgb="002A4D7C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
-        <bgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,20 +84,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,17 +457,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="9433" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -537,163 +517,6 @@
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Failure Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>TC_GEN_002</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>test_auth_invalid_credentials</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>27.76</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-24 01:32:38</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="8df9b57d-e778-4b63-9dc7-3ab099e509dd")&gt;
-    def test_auth_invalid_credentials(driver):
-        """Test that login with invalid credentials displays an error on mobile."""
-        time.sleep(3)
-        login_page = LoginPage(driver)
-&gt;       login_page.login("nonexistent_farmer@kisan.com", "WrongPass123!")
-tests/mobile_e2e/test_suites/test_auth.py:25: 
-_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
-tests/mobile_e2e/pages/login_page.py:14: in login
-    self.send_keys(self.EMAIL_INPUT, email)
-tests/mobile_e2e/pages/base_page.py:31: in send_keys
-    element = self.wait_for_element(locator)
-              ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-tests/mobile_e2e/pages/base_page.py:22: in wait_for_element
-    raise e
-tests/mobile_e2e/pages/base_page.py:17: in wait_for_element
-    return WebDriverWait(self.driver, self.timeout).until(
-/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/support/wait.py:112: in until
-    value = method(self._driver)
-            ^^^^^^^^^^^^^^^^^^^^
-/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/support/expected_conditions.py:188: in _predicate
-    return _element_if_visible(driver.find_element(*locator))
-                               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:899: in find_element
-    return self.execute(Command.FIND_ELEMENT, {"using": by, "value": value})["value"]
-           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:492: in execute
-    self.error_handler.check_response(response)
-_ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
-self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7f2b9cc46990&gt;
-response = {'status': 500, 'value': '{"value":{"error":"unknown error","message":"io.appium.uiautomator2.common.exceptions.UiAuto...r2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath1(AccessibilityNodeInfoDumper.java:279)\\n\\t... 33 more\\n"}}'}
-    def check_response(self, response: Dict[str, Any]) -&gt; None:
-        """
-        https://www.w3.org/TR/webdriver/#errors
-        """
-        payload = response.get('value', '')
-        if isinstance(payload, dict):
-            payload_dict = payload
-        else:
-            try:
-                payload_dict = json.loads(payload)
-            except (json.JSONDecodeError, TypeError):
-                return
-            if not isinstance(payload_dict, dict):
-                return
-        value = payload_dict.get('value')
-        if not isinstance(value, dict):
-            return
-        error = value.get('error')
-        if not error:
-            return
-        message = value.get('message', error)
-        stacktrace = value.get('stacktrace', '')
-        # In theory, we should also be checking HTTP status codes.
-        # Java client, for example, prints a warning if the actual `error`
-        # value does not match to the response's HTTP status code.
-        exception_class: Type[sel_exceptions.WebDriverException] = ERROR_TO_EXC_MAPPING.get(
-            error, sel_exceptions.WebDriverException
-        )
-        if exception_class is sel_exceptions.WebDriverException and message:
-            if message == 'No such context found.':
-                exception_class = appium_exceptions.NoSuchContextException
-            elif message == 'That command could not be executed in the current context.':
-                exception_class = appium_exceptions.InvalidSwitchToTargetException
-        if exception_class is sel_exceptions.UnexpectedAlertPresentException:
-            raise sel_exceptions.UnexpectedAlertPresentException(
-                msg=message,
-                stacktrace=format_stacktrace(stacktrace),
-                alert_text=value.get('data'),
-            )
-&gt;       raise exception_class(msg=message, stacktrace=format_stacktrace(stacktrace))
-E       selenium.common.exceptions.WebDriverException: Message: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
-E       Stacktrace:
-E       io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
-E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath1(AccessibilityNodeInfoDumper.java:306)
-E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodes(AccessibilityNodeInfoDumper.java:377)
-E       	at io.appium.uiautomator2.utils.ElementLocationHelpers.getXPathNodeMatch(ElementLocationHelpers.java:124)
-E       	at io.appium.uiautomator2.utils.ElementLocationHelpers.findElement(ElementLocationHelpers.java:151)
-E       	at io.appium.uiautomator2.handler.FindElement.safeHandle(FindElement.java:60)
-E       	at io.appium.uiautomator2.handler.request.SafeRequestHandler.handle(SafeRequestHandler.java:59)
-E       	at io.appium.uiautomator2.server.AppiumServlet.handleRequest(AppiumServlet.java:267)
-E       	at io.appium.uiautomator2.server.AppiumServlet.handleHttpRequest(AppiumServlet.java:261)
-E       	at io.appium.uiautomator2.http.ServerHandler.channelRead(ServerHandler.java:77)
-E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:357)
-E       	at io.netty.handler.codec.MessageToMessageDecoder.channelRead(MessageToMessageDecoder.java:107)
-E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:357)
-E       	at io.netty.channel.CombinedChannelDuplexHandler$DelegatingChannelHandlerContext.fireChannelRead(CombinedChannelDuplexHandler.java:434)
-E       	at io.netty.handler.codec.ByteToMessageDecoder.fireChannelRead(ByteToMessageDecoder.java:361)
-E       	at io.netty.handler.codec.ByteToMessageDecoder.channelRead(ByteToMessageDecoder.java:325)
-E       	at io.netty.channel.CombinedChannelDuplexHandler.channelRead(CombinedChannelDuplexHandler.java:249)
-E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:355)
-E       	at io.netty.handler.timeout.IdleStateHandler.channelRead(IdleStateHandler.java:288)
-E       	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:355)
-E       	at io.netty.channel.DefaultChannelPipeline$HeadContext.channelRead(DefaultChannelPipeline.java:1429)
-E       	at io.netty.channel.DefaultChannelPipeline.fireChannelRead(DefaultChannelPipeline.java:918)
-E       	at io.netty.channel.nio.AbstractNioByteChannel$NioByteUnsafe.read(AbstractNioByteChannel.java:176)
-E       	at io.netty.channel.nio.AbstractNioChannel$AbstractNioUnsafe.handle(AbstractNioChannel.java:445)
-E       	at io.netty.channel.nio.NioIoHandler$DefaultNioRegistration.handle(NioIoHandler.java:388)
-E       	at io.netty.channel.nio.NioIoHandler.processSelectedKey(NioIoHandler.java:596)
-E       	at io.netty.channel.nio.NioIoHandler.processSelectedKeysOptimized(NioIoHandler.java:571)
-E       	at io.netty.channel.nio.NioIoHandler.processSelectedKeys(NioIoHandler.java:512)
-E       	at io.netty.channel.nio.NioIoHandler.run(NioIoHandler.java:484)
-E       	at io.netty.channel.SingleThreadIoEventLoop.runIo(SingleThreadIoEventLoop.java:225)
-E       	at io.netty.channel.SingleThreadIoEventLoop.run(SingleThreadIoEventLoop.java:196)
-E       	at io.netty.util.concurrent.SingleThreadEventExecutor$5.run(SingleThreadEventExecutor.java:1195)
-E       	at io.netty.util.internal.ThreadExecutorMap$2.run(ThreadExecutorMap.java:74)
-E       	at io.netty.util.concurrent.FastThreadLocalRunnable.run(FastThreadLocalRunnable.java:30)
-E       	at java.lang.Thread.run(Thread.java:919)
-E       Caused by: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
-E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getActiveWindowRoot(AXWindowHelpers.java:107)
-E       	at io.appium.uiautomator2.utils.AXWindowHelpers.retrieveWindowRoots(AXWindowHelpers.java:87)
-E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getCachedWindowRoots(AXWindowHelpers.java:68)
-E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.toStream(AccessibilityNodeInfoDumper.java:228)
-E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath1(AccessibilityNodeInfoDumper.java:279)
-E       	... 33 more
-/opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/appium/webdriver/errorhandler.py:125: WebDriverException</t>
         </is>
       </c>
     </row>
